--- a/Input/Allianz_Expat_Protect/benefits1.xlsx
+++ b/Input/Allianz_Expat_Protect/benefits1.xlsx
@@ -271,7 +271,7 @@
     <t xml:space="preserve">Annually</t>
   </si>
   <si>
-    <t xml:space="preserve">Zone 2</t>
+    <t xml:space="preserve">Nzone2</t>
   </si>
   <si>
     <t xml:space="preserve">Out-patient Consultations/Out-patient Specialists/Out-patient Medicines/Vaccination/Scans &amp; Diagnostic Tests/Physiotherapy/Optical Benefits/Wellness &amp; Health Screening/Alternative Medicines/Mental Health Benefit</t>
@@ -429,7 +429,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BD13"/>
-  <sheetFormatPr defaultColWidth="8.51953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5234375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="8.5"/>
   </cols>
@@ -600,7 +600,7 @@
       <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="0" t="s">
+      <c r="BD1" s="2" t="s">
         <v>55</v>
       </c>
     </row>
@@ -770,7 +770,7 @@
       <c r="BC2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="BD2" s="0" t="s">
+      <c r="BD2" s="2" t="s">
         <v>87</v>
       </c>
     </row>
